--- a/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.8/backtests/window_40/return_r2/post_rank_positive_return/staggered_10_accounts_hold_10d/close/close_annual_metrics.xlsx
@@ -466,10 +466,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.05978206779160034</v>
+        <v>-0.1411908253052691</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2981783543098615</v>
+        <v>0.182347463227969</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.1347759275448206</v>
+        <v>-0.9331287281414478</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>-0.1849561657046134</v>
+        <v>-1.168587479174762</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2893277907322577</v>
+        <v>0.2118161004283193</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-0.2325705712453166</v>
+        <v>-0.7460381971078474</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>11.53420087862867</v>
+        <v>10.04413960575912</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.2078769534626754</v>
+        <v>-0.1506336171388424</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2309886230633278</v>
+        <v>0.2564200366718286</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-0.9989278976064834</v>
+        <v>-0.5930931006065133</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.302690222418598</v>
+        <v>-0.8170984215352622</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.2630505016078087</v>
+        <v>0.2750145437411621</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8191136046439366</v>
+        <v>-0.5684956006804153</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>12.80858021398405</v>
+        <v>11.74073320424018</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.05417435326578623</v>
+        <v>-0.1128040152127796</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.2256306549411164</v>
+        <v>0.2064703257139628</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>-0.2108173845849902</v>
+        <v>-0.5725128795417419</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-0.3043915093653503</v>
+        <v>-0.7749358445378234</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2443611962923378</v>
+        <v>0.2396747083608287</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.230595926705741</v>
+        <v>-0.4889173069444122</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>12.47320071184351</v>
+        <v>12.52897340896638</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.08731650734552776</v>
+        <v>0.07964429061635281</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2216462904832094</v>
+        <v>0.2680748872849573</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4363047507310417</v>
+        <v>0.375093842321506</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.6411399564129284</v>
+        <v>0.5532024224450511</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1601885996497235</v>
+        <v>0.1781871498693361</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.5686064446041137</v>
+        <v>0.4661868535587524</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>13.15899853630196</v>
+        <v>14.79914479437478</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3782850501362507</v>
+        <v>0.5670946823848591</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2667403867397303</v>
+        <v>0.3006076292958307</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.32639431071094</v>
+        <v>1.652480840278533</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.855352544039108</v>
+        <v>2.370312326488668</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1695033890403355</v>
+        <v>0.1828890793498668</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.328926046101508</v>
+        <v>3.244512812811822</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>14.12210172765612</v>
+        <v>12.06036323848598</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.09786618672958292</v>
+        <v>0.1773476257615245</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3629955473914564</v>
+        <v>0.3792596038756097</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.6061692388061907</v>
+        <v>0.9300784586388823</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8708483308432795</v>
+        <v>1.343763510679423</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2430581481799127</v>
+        <v>0.1744461834709038</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7588416647390318</v>
+        <v>1.974570254288615</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>11.8809616038798</v>
+        <v>11.91740283078989</v>
       </c>
     </row>
   </sheetData>
